--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0208.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0208.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Bình minh của nỗ lực bền bỉ. Một đôi găng tay được chế tạo dành cho Cộng Hưởng Giả mới. Ẩn chứa bên trong vẻ ngoài giản đơn là một sức mạnh không thể xem thường.</t>
+          <t>Bình minh của nỗ lực bền bỉ. Một đôi găng tay được chế tạo dành cho Resonator mới. Ẩn chứa bên trong vẻ ngoài giản đơn là một sức mạnh không thể xem thường.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Nguồn gốc của sự khởi đầu vĩnh hằng. Một Bộ Chỉnh Lưu được thiết kế cho Cộng Hưởng Giả mới. Ẩn chứa bên trong vẻ ngoài đơn giản là một sức mạnh không thể xem thường.</t>
+          <t>Nguồn gốc của sự khởi đầu vĩnh hằng. Một Bộ Chỉnh Lưu được thiết kế cho Resonator mới. Ẩn chứa bên trong vẻ ngoài đơn giản là một sức mạnh không thể xem thường.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Nguồn gốc của sự khởi đầu vĩnh hằng. Một Bộ Chỉnh Lưu được thiết kế cho Cộng Hưởng Giả mới. Ẩn chứa bên trong vẻ ngoài đơn giản là một sức mạnh không thể xem thường.</t>
+          <t>Nguồn gốc của sự khởi đầu vĩnh hằng. Một Bộ Chỉnh Lưu được thiết kế cho Resonator mới. Ẩn chứa bên trong vẻ ngoài đơn giản là một sức mạnh không thể xem thường.</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Nguồn gốc của sự khởi đầu vĩnh hằng. Một Bộ Chỉnh Lưu được thiết kế cho Cộng Hưởng Giả mới. Ẩn chứa bên trong vẻ ngoài đơn giản là một sức mạnh không thể xem thường.</t>
+          <t>Nguồn gốc của sự khởi đầu vĩnh hằng. Một Bộ Chỉnh Lưu được thiết kế cho Resonator mới. Ẩn chứa bên trong vẻ ngoài đơn giản là một sức mạnh không thể xem thường.</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Thu thập 4.000 Điểm Mở Rộng Điểm Kỳ Dị trong một trận đấu với đội gồm các Cộng Hưởng Giả đã tăng cường</t>
+          <t>Thu thập 4.000 Điểm Mở Rộng Điểm Kỳ Dị trong một trận đấu với đội gồm các Resonator đã tăng cường</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>&lt;color=#ffcd23&gt;This is a high-difficulty challenge. Please be fully prepared.&lt;/color&gt;</t>
+          <t>&lt;color=#ffcd23&gt;Đây là thử thách cực kỳ khó. Hãy chuẩn bị kỹ càng trước khi bắt đầu.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -9355,7 +9355,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Một cuộc gọi đã chấm dứt kỳ nghỉ mà cậu hằng mong đợi.</t>
+          <t>Một cuộc gọi đã chấm dứt kỳ nghỉ mà mày hằng mong đợi.</t>
         </is>
       </c>
     </row>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Dùng 100 Mảnh Giấc Mơ để mở Cửa Hàng Tuyển Dụng Đặc Biệt với các Cộng Hưởng Giả cùng Thuộc Tính.</t>
+          <t>Dùng 100 Mảnh Giấc Mơ để mở Cửa Hàng Tuyển Dụng Đặc Biệt với các Resonator cùng Thuộc Tính.</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Mr. Sunglasses [Information Broker]</t>
+          <t>Ông Kính Đen [Người môi giới thông tin]</t>
         </is>
       </c>
     </row>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>Cái gì cơ???</t>
         </is>
       </c>
     </row>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>"(Ngáp)... Ta ngủ bao lâu thế... Ngươi nói gì hả, Chixia?"</t>
+          <t>"(Ngáp)... Tao ngủ bao lâu thế... Mày nói gì hả, Chixia?"</t>
         </is>
       </c>
     </row>
@@ -18331,7 +18331,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>"Phù... Cô ấy bận tối mắt tối mũi rồi nhỉ? Thấy chưa? Ta bảo rồi, làm sĩ quan vất vả lắm đấy."</t>
+          <t>"Phù... Cô ấy bận tối mắt tối mũi rồi nhỉ? Thấy chưa? Tao bảo rồi, làm sĩ quan vất vả lắm đấy."</t>
         </is>
       </c>
     </row>
@@ -18656,7 +18656,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>"Thấy chưa, ta vừa nói gì... Đợi đã, ngươi đi đâu thế?"</t>
+          <t>"Thấy chưa, tao vừa nói gì... Đợi đã, mày đi đâu thế?"</t>
         </is>
       </c>
     </row>
@@ -18721,7 +18721,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>"Giúp cô ấy chứ còn gì! Ta không để cô ấy một mình chiến đấu với con quái vật đó đâu!"</t>
+          <t>"Giúp cô ấy chứ còn gì! Tao không để cô ấy một mình chiến đấu với con quái vật đó đâu!"</t>
         </is>
       </c>
     </row>
@@ -19826,7 +19826,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>"Ừ. Dù là phiên bản Baizhi nào đi nữa, ta cũng chả hiểu nàng ta đang nói cái quái gì..."</t>
+          <t>"Ừ. Dù là phiên bản Baizhi nào đi nữa, tao cũng chả hiểu nàng ta đang nói cái quái gì..."</t>
         </is>
       </c>
     </row>
@@ -20281,7 +20281,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>"Được rồi, được rồi. Cậu lại nhìn ta kiểu đó nữa rồi. Ta hiểu mà. Ta không nóng nảy như cậu nghĩ đâu... Ta sẽ đi nghỉ đây."</t>
+          <t>"Được rồi, được rồi. Cậu lại nhìn tao kiểu đó nữa rồi. Tao hiểu mà. Tao không nóng nảy như cậu nghĩ đâu... Tao sẽ đi nghỉ đây."</t>
         </is>
       </c>
     </row>
@@ -21776,7 +21776,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>"Thật lòng mà nói, ta sợ lắm. Từ cái lần bị lão bác sĩ mắng cho một trận ấy. Sợ rằng mình sẽ biến thành một trong những thứ đó thật."</t>
+          <t>"Thật lòng mà nói, tao sợ lắm. Từ cái lần bị lão bác sĩ mắng cho một trận ấy. Sợ rằng mình sẽ biến thành một trong những thứ đó thật."</t>
         </is>
       </c>
     </row>
@@ -22491,7 +22491,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>"Giấy phạt tốc độ là gì? Viết tắt của 'giấy phạt ăn nhanh' hả? Ta cá là ta có thể rinh cái cúp đó về nhà!"</t>
+          <t>"Giấy phạt tốc độ là gì? Viết tắt của 'giấy phạt ăn nhanh' hả? Tao cá là tao có thể rinh cái cúp đó về nhà!"</t>
         </is>
       </c>
     </row>
@@ -25026,7 +25026,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>"Được rồi, giờ ta hiểu rồi..."</t>
+          <t>"Được rồi, giờ tao hiểu rồi..."</t>
         </is>
       </c>
     </row>
@@ -27756,7 +27756,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Cậu cũng tham gia cứu hộ à?</t>
+          <t>Mày cũng tham gia cứu hộ à?</t>
         </is>
       </c>
     </row>
@@ -30031,7 +30031,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>"Ừ. Ừm. Giờ thì ta hoàn toàn hiểu rồi." Abby gật đầu đầy tự tin.</t>
+          <t>"Ừ. Ừm. Giờ thì tao hoàn toàn hiểu rồi." Abby gật đầu đầy tự tin.</t>
         </is>
       </c>
     </row>
@@ -30616,7 +30616,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>"Phù... Ta hoàn toàn đồng ý với cậu. Chỉ cần nằm đây phơi nắng thôi cũng đã sướng rồi... Nhưng mà có đồ ăn vặt nhấm nháp thì còn gì bằng."</t>
+          <t>"Phù... Tao hoàn toàn đồng ý với cậu. Chỉ cần nằm đây phơi nắng thôi cũng đã sướng rồi... Nhưng mà có đồ ăn vặt nhấm nháp thì còn gì bằng."</t>
         </is>
       </c>
     </row>
